--- a/mario/test/supporting_files/add_sectors/add_sector_iot_template.xlsx
+++ b/mario/test/supporting_files/add_sectors/add_sector_iot_template.xlsx
@@ -496,7 +496,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,14 +509,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Reg1</t>
+          <t>r1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Reg2</t>
+          <t>r2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>r3</t>
         </is>
       </c>
     </row>
@@ -552,7 +559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -580,12 +587,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>s1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>M EUR</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -597,12 +604,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Services</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>M EUR</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -614,29 +621,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Industry</t>
+          <t>s3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>M EUR</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Factor of production</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Taxes</t>
+          <t>s4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>M EUR</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
@@ -648,63 +655,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Wages</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>M EUR</t>
+          <t>EUR</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Factor of production</t>
+          <t>Satellite account</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capital</t>
+          <t>None</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>M EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Satellite account</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Employment</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1000 p</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Satellite account</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>CO2</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>kg</t>
+          <t>ton</t>
         </is>
       </c>
     </row>
